--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -1012,7 +1012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H21"/>
+  <dimension ref="C1:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1354,9 +1354,26 @@
         <v>900000</v>
       </c>
     </row>
+    <row r="22" customHeight="1" spans="3:7">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>651</v>
+      </c>
+      <c r="E22" s="1">
+        <v>700</v>
+      </c>
+      <c r="F22" s="1">
+        <v>177000000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1000000</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:G2 D3:G3 E4:G4 E5:G5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:G2 C3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1012,8 +1012,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="C1:G24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="5" width="8.75" style="1" customWidth="1"/>
@@ -1217,7 +1217,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:8">
+    <row r="14" customHeight="1" spans="3:7">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1233,7 +1233,6 @@
       <c r="G14" s="2">
         <v>200000</v>
       </c>
-      <c r="H14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="3:7">
       <c r="C15" s="2">
@@ -1371,9 +1370,45 @@
         <v>1000000</v>
       </c>
     </row>
+    <row r="23" customHeight="1" spans="3:7">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>701</v>
+      </c>
+      <c r="E23" s="1">
+        <v>750</v>
+      </c>
+      <c r="F23" s="1">
+        <f>F22+G22*50</f>
+        <v>227000000</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:7">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>751</v>
+      </c>
+      <c r="E24" s="1">
+        <v>800</v>
+      </c>
+      <c r="F24" s="1">
+        <f>F23+G23*50</f>
+        <v>302000000</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2000000</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:G2 C3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -1012,7 +1012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G24"/>
+  <dimension ref="C1:G25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1381,7 +1381,7 @@
         <v>750</v>
       </c>
       <c r="F23" s="1">
-        <f>F22+G22*50</f>
+        <f t="shared" ref="F23:F25" si="0">F22+G22*50</f>
         <v>227000000</v>
       </c>
       <c r="G23" s="1">
@@ -1399,11 +1399,29 @@
         <v>800</v>
       </c>
       <c r="F24" s="1">
-        <f>F23+G23*50</f>
+        <f t="shared" si="0"/>
         <v>302000000</v>
       </c>
       <c r="G24" s="1">
         <v>2000000</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:7">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>801</v>
+      </c>
+      <c r="E25" s="1">
+        <v>900</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="0"/>
+        <v>402000000</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3000000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t>_id</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>long</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1015,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1381,7 +1384,7 @@
         <v>750</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" ref="F23:F25" si="0">F22+G22*50</f>
+        <f t="shared" ref="F23:F27" si="0">F22+G22*50</f>
         <v>227000000</v>
       </c>
       <c r="G23" s="1">
@@ -1422,6 +1425,48 @@
       </c>
       <c r="G25" s="1">
         <v>3000000</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:7">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>901</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="0"/>
+        <v>552000000</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:7">
+      <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1100</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="0"/>
+        <v>752000000</v>
+      </c>
+      <c r="G27" s="1">
+        <v>5000000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1438,8 +1438,8 @@
         <v>1000</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="0"/>
-        <v>552000000</v>
+        <f>F25+G25*100</f>
+        <v>702000000</v>
       </c>
       <c r="G26" s="1">
         <v>4000000</v>
@@ -1462,8 +1462,8 @@
         <v>1100</v>
       </c>
       <c r="F27" s="1">
-        <f t="shared" si="0"/>
-        <v>752000000</v>
+        <f>F26+G26*100</f>
+        <v>1102000000</v>
       </c>
       <c r="G27" s="1">
         <v>5000000</v>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
     <t>_id</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>long</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G27"/>
+  <dimension ref="C1:G28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1438,20 +1435,14 @@
         <v>1000</v>
       </c>
       <c r="F26" s="1">
-        <f>F25+G25*100</f>
+        <f t="shared" ref="F26:F28" si="1">F25+G25*100</f>
         <v>702000000</v>
       </c>
       <c r="G26" s="1">
         <v>4000000</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:7">
-      <c r="A27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
+    <row r="27" customHeight="1" spans="3:7">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1459,14 +1450,32 @@
         <v>1001</v>
       </c>
       <c r="E27" s="1">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="F27" s="1">
-        <f>F26+G26*100</f>
-        <v>1102000000</v>
+        <f>F26+G26*200</f>
+        <v>1502000000</v>
       </c>
       <c r="G27" s="1">
-        <v>5000000</v>
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:7">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1201</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1400</v>
+      </c>
+      <c r="F28" s="1">
+        <f>F27+G27*200</f>
+        <v>2702000000</v>
+      </c>
+      <c r="G28" s="1">
+        <v>8000000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -1012,7 +1012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G28"/>
+  <dimension ref="C1:G29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1453,7 +1453,7 @@
         <v>1200</v>
       </c>
       <c r="F27" s="1">
-        <f>F26+G26*200</f>
+        <f t="shared" ref="F27:F30" si="2">F26+G26*200</f>
         <v>1502000000</v>
       </c>
       <c r="G27" s="1">
@@ -1471,11 +1471,29 @@
         <v>1400</v>
       </c>
       <c r="F28" s="1">
-        <f>F27+G27*200</f>
+        <f t="shared" si="2"/>
         <v>2702000000</v>
       </c>
       <c r="G28" s="1">
         <v>8000000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:7">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1401</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1700</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="2"/>
+        <v>4302000000</v>
+      </c>
+      <c r="G29" s="1">
+        <v>10000000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -1012,7 +1012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G29"/>
+  <dimension ref="C1:G30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1496,6 +1496,24 @@
         <v>10000000</v>
       </c>
     </row>
+    <row r="30" customHeight="1" spans="3:7">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1701</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="2"/>
+        <v>6302000000</v>
+      </c>
+      <c r="G30" s="1">
+        <v>13000000</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:G5" errorStyle="warning">
